--- a/output/2026-09-14_19_Croazia_Licko-senjska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-14_19_Croazia_Licko-senjska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SCARTATA: rivenditore generalista di materiali edili, ferramenta, colori/vernici e merci miste (attivo dal 1990, 3-4 punti vendita). Vende marginalmente vernici per metallo ma non è distributore specializzato in utensili/macchine/forniture per lavorazione metalli. Fuori target settore Metalworking.</t>
+          <t>SCARTATA: rivenditore generalista di materiali edili, ferramenta, colori/vernici e merci miste (attivo dal 1990, 3-4 punti vendita). Vende marginalmente vernici per metallo ma non è distributore specializzato in utensili/macchine/forniture per lavorazione metalli. Fuori target settore Metalworking. [DUPLICATO — vedi anche: 2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
